--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/incidentes_seguranca.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/incidentes_seguranca.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Documents\GitHub\Arquivado\Faculdade\Terceiro Semestre\Estatística Aplicada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAC1285-0FEA-4299-A39D-1B64BFA75157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD29A5E-D39D-4A0C-ACEE-CEBBAA24C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TI x TR, TI x SA" sheetId="10" r:id="rId1"/>
-    <sheet name="Incidentes de Segurança" sheetId="1" r:id="rId2"/>
-    <sheet name="Gráficos" sheetId="5" r:id="rId3"/>
-    <sheet name="BoxPlot" sheetId="3" r:id="rId4"/>
-    <sheet name="Dispersão" sheetId="4" r:id="rId5"/>
+    <sheet name="Incidentes de Segurança" sheetId="1" r:id="rId1"/>
+    <sheet name="Gráficos" sheetId="5" r:id="rId2"/>
+    <sheet name="BoxPlot" sheetId="3" r:id="rId3"/>
+    <sheet name="Dispersão" sheetId="4" r:id="rId4"/>
+    <sheet name="TI x TR, TI x SA" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Gráficos!$K$3:$K$8</definedName>
@@ -31,8 +31,10 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
-    <pivotCache cacheId="16" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -229,10 +231,37 @@
     <t>Quantitativa discreta</t>
   </si>
   <si>
-    <t>Rótulos de Linha</t>
+    <t>1-11</t>
   </si>
   <si>
-    <t>Soma de Tempo de Resolução (h)</t>
+    <t>11-21</t>
+  </si>
+  <si>
+    <t>21-31</t>
+  </si>
+  <si>
+    <t>31-41</t>
+  </si>
+  <si>
+    <t>Média de Tempo de Resolução (h)</t>
+  </si>
+  <si>
+    <t>Rótulos de Coluna</t>
+  </si>
+  <si>
+    <t>Média de Sistemas Afetados</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>11-20</t>
+  </si>
+  <si>
+    <t>21-30</t>
+  </si>
+  <si>
+    <t>31-40</t>
   </si>
 </sst>
 </file>
@@ -566,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -665,14 +694,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -719,50 +800,282 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="90">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5413,13 +5726,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>317500</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>88899</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>502684</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>46739</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5434,8 +5747,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5765800" y="88900"/>
-          <a:ext cx="9291084" cy="4205989"/>
+          <a:off x="5518150" y="88899"/>
+          <a:ext cx="10100709" cy="7064376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5521,6 +5834,195 @@
           <a:r>
             <a:rPr lang="pt-BR" sz="1200">
               <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Com</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> base nos cálculos do </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tempo de Resolução (Horas)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> e </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sistemas Afetados</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>a) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tempo de Resolução</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> existe moda? Justifique.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="95000"/>
+                  <a:lumOff val="5000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:effectLst/>
@@ -5528,7 +6030,172 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>1) </a:t>
+            <a:t>Não, pois não há nenhum número que se repita dentro da sequência.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:endParaRPr lang="pt-BR" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>b) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Na</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> variável </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sistemas Afetados</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, os dados são homogêneos ou heterogêneos? Justifique.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>São homogêneos, pois a diferença entra a média e o desvio padrão é pequena.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="1200">
@@ -5552,11 +6219,46 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> com maior número de casos? Com base na quantidade desse tipo de incidente, Justifique.</a:t>
+            <a:t> com maior número de casos? Com base na quantidade desse tipo de incidente, a empresa deveria se esforçar principalmente só com ele? Justifique.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sim, o incidente com maior número de casos é o de Phishing. Não, porque mesmo sendo o maior incidente com maior número de casos foi apenas necessário o menor tempo de resolução para ser resolvido e não atingiu muitos sistemas possuindo menor número de sistemas afetados. A empresa deve na verdade focar nos incidentes de Vazamentos de Dados e de Malware, que possuem maior número de sistemas afetados e precisam de maior tempo de resolução para serem arrumadas.</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:solidFill>
-              <a:schemeClr val="tx1"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -5597,14 +6299,14 @@
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>2) </a:t>
+            <a:t>3) </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
@@ -5716,7 +6418,7 @@
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -5735,7 +6437,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Qual tipo de incidente teve, em média, maior tempo de resolução e maior numero de sistemas afetados? </a:t>
+            <a:t>Qual tipo de incidente teve, em média, maior tempo de resolução e maior quantidade de sistemas afetados? </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
@@ -5747,17 +6449,76 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>A diferença de médias em tempo de resolução e sistemas afetados é grande o suficiente para ser alarmante á empresa? </a:t>
+            <a:t>A diferença desse incidente comparado aos outros incidentes é grande o suficiente para ser um problema sério para a empresa? </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1400">
-            <a:effectLst/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>O tipo de incidente que teve maior tempo de resolução e maior quantidade de sistemas afetados é o de Vazamento de Dados. Sim, pois ele possui o maior número de tempo de resolução e de sistemas afetados por uma grande margem.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:endParaRPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
             <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -5770,7 +6531,7 @@
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -5851,6 +6612,30 @@
         </a:p>
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>A categoria que de tempo de resolução de horas que possui o menor número de sistemas afetados é de 1-11 horas.</a:t>
+          </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
@@ -5863,12 +6648,6 @@
         </a:p>
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
-          <a:endParaRPr lang="pt-BR" sz="1200" b="1">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
           <a:endParaRPr lang="pt-BR" sz="1100" b="0" cap="none" spc="0">
             <a:ln w="0"/>
             <a:solidFill>
@@ -5884,19 +6663,60 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-BR" sz="1100" b="0" cap="none" spc="0">
-            <a:ln w="0"/>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>4) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Faça</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> os gráficos de BoxPlot e Dispersão. Qual é a correlação linear, ela é positiva ou negativa? Há outliers? A presença desses outliers afetam grandemente a correlação? Justifique.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>R: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>A correlação linear é 0,99, sendo fortemente positiva. Há dois outliers, apesar de haver dois outliers a correlação persistiu pois ele segre o padrão estabelecido onde quanto mais sistemas afetados por um incidente tiver maior sera o tempo de resolução, fazendo com que eles fiquem no mesmo sentido.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0">
             <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:effectLst>
-              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                <a:schemeClr val="dk1">
-                  <a:alpha val="40000"/>
-                </a:schemeClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5991,8 +6811,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8458200" y="2330450"/>
-              <a:ext cx="3187700" cy="2108200"/>
+              <a:off x="8655050" y="2406650"/>
+              <a:ext cx="3187700" cy="2184400"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6069,8 +6889,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6226175" y="2336800"/>
-              <a:ext cx="2212975" cy="2139950"/>
+              <a:off x="6423025" y="2413000"/>
+              <a:ext cx="2212975" cy="2216150"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6152,8 +6972,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="609600" y="184150"/>
-              <a:ext cx="3149600" cy="2743200"/>
+              <a:off x="609600" y="190500"/>
+              <a:ext cx="3149600" cy="2832100"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6230,8 +7050,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4267200" y="184150"/>
-              <a:ext cx="3054350" cy="2743200"/>
+              <a:off x="4267200" y="190500"/>
+              <a:ext cx="3054350" cy="2832100"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6440,7 +7260,59 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Tempo de Resolução (h)" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1" maxValue="37.200000000000003"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1" maxValue="37.200000000000003" count="40">
+        <n v="1.3"/>
+        <n v="2.7"/>
+        <n v="1.8"/>
+        <n v="3.4"/>
+        <n v="1"/>
+        <n v="4.2"/>
+        <n v="2.1"/>
+        <n v="5.8"/>
+        <n v="1.6"/>
+        <n v="3.1"/>
+        <n v="2.4"/>
+        <n v="1.9"/>
+        <n v="4.7"/>
+        <n v="2.2999999999999998"/>
+        <n v="1.4"/>
+        <n v="3.8"/>
+        <n v="5.2"/>
+        <n v="2.8"/>
+        <n v="1.7"/>
+        <n v="6.1"/>
+        <n v="2.2000000000000002"/>
+        <n v="3.6"/>
+        <n v="4.0999999999999996"/>
+        <n v="7.3"/>
+        <n v="14.5"/>
+        <n v="6.2"/>
+        <n v="22"/>
+        <n v="9.8000000000000007"/>
+        <n v="21.5"/>
+        <n v="11.4"/>
+        <n v="17.2"/>
+        <n v="8.6"/>
+        <n v="4.8"/>
+        <n v="12.3"/>
+        <n v="7.6"/>
+        <n v="19.399999999999999"/>
+        <n v="9.1"/>
+        <n v="15.7"/>
+        <n v="31.5"/>
+        <n v="37.200000000000003"/>
+      </sharedItems>
+      <fieldGroup base="2">
+        <rangePr startNum="1" endNum="37.200000000000003" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;1"/>
+          <s v="1-11"/>
+          <s v="11-21"/>
+          <s v="21-31"/>
+          <s v="31-41"/>
+          <s v="&gt;41"/>
+        </groupItems>
+      </fieldGroup>
     </cacheField>
     <cacheField name="Sistemas Afetados" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="33"/>
@@ -6454,6 +7326,180 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Elio Savoine" refreshedDate="46155.691491550926" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{C5EA8E8F-C658-4B4E-9351-07DC3B71FD0F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D41" sheet="Incidentes de Segurança"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
+    </cacheField>
+    <cacheField name="Tipo de Incidente" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Phishing"/>
+        <s v="Malware"/>
+        <s v="Acesso Não Autorizado"/>
+        <s v="Vazamento de Dados"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Tempo de Resolução (h)" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1" maxValue="37.200000000000003"/>
+    </cacheField>
+    <cacheField name="Sistemas Afetados" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="33" count="17">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="12"/>
+        <n v="18"/>
+        <n v="8"/>
+        <n v="17"/>
+        <n v="10"/>
+        <n v="14"/>
+        <n v="7"/>
+        <n v="15"/>
+        <n v="13"/>
+        <n v="28"/>
+        <n v="33"/>
+      </sharedItems>
+      <fieldGroup base="3">
+        <rangePr startNum="1" endNum="33" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;1"/>
+          <s v="1-10"/>
+          <s v="11-20"/>
+          <s v="21-30"/>
+          <s v="31-40"/>
+          <s v="&gt;41"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Elio Savoine" refreshedDate="46155.731982060184" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{481DFD8E-1072-4598-B28A-3DF8B7D1F876}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D41" sheet="Incidentes de Segurança"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
+    </cacheField>
+    <cacheField name="Tipo de Incidente" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Phishing"/>
+        <s v="Malware"/>
+        <s v="Acesso Não Autorizado"/>
+        <s v="Vazamento de Dados"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Tempo de Resolução (h)" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1" maxValue="37.200000000000003" count="40">
+        <n v="1.3"/>
+        <n v="2.7"/>
+        <n v="1.8"/>
+        <n v="3.4"/>
+        <n v="1"/>
+        <n v="4.2"/>
+        <n v="2.1"/>
+        <n v="5.8"/>
+        <n v="1.6"/>
+        <n v="3.1"/>
+        <n v="2.4"/>
+        <n v="1.9"/>
+        <n v="4.7"/>
+        <n v="2.2999999999999998"/>
+        <n v="1.4"/>
+        <n v="3.8"/>
+        <n v="5.2"/>
+        <n v="2.8"/>
+        <n v="1.7"/>
+        <n v="6.1"/>
+        <n v="2.2000000000000002"/>
+        <n v="3.6"/>
+        <n v="4.0999999999999996"/>
+        <n v="7.3"/>
+        <n v="14.5"/>
+        <n v="6.2"/>
+        <n v="22"/>
+        <n v="9.8000000000000007"/>
+        <n v="21.5"/>
+        <n v="11.4"/>
+        <n v="17.2"/>
+        <n v="8.6"/>
+        <n v="4.8"/>
+        <n v="12.3"/>
+        <n v="7.6"/>
+        <n v="19.399999999999999"/>
+        <n v="9.1"/>
+        <n v="15.7"/>
+        <n v="31.5"/>
+        <n v="37.200000000000003"/>
+      </sharedItems>
+      <fieldGroup base="2">
+        <rangePr startNum="1" endNum="37.200000000000003" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;1"/>
+          <s v="1-11"/>
+          <s v="11-21"/>
+          <s v="21-31"/>
+          <s v="31-41"/>
+          <s v="&gt;41"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Sistemas Afetados" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="33" count="17">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="12"/>
+        <n v="18"/>
+        <n v="8"/>
+        <n v="17"/>
+        <n v="10"/>
+        <n v="14"/>
+        <n v="7"/>
+        <n v="15"/>
+        <n v="13"/>
+        <n v="28"/>
+        <n v="33"/>
+      </sharedItems>
+      <fieldGroup base="3">
+        <rangePr startNum="1" endNum="33" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;1"/>
+          <s v="1-10"/>
+          <s v="11-20"/>
+          <s v="21-30"/>
+          <s v="31-40"/>
+          <s v="&gt;41"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
   <r>
@@ -6664,432 +7710,738 @@
   <r>
     <n v="1"/>
     <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <x v="0"/>
+    <x v="15"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <x v="0"/>
+    <x v="16"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <x v="0"/>
+    <x v="17"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <x v="0"/>
+    <x v="18"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <x v="0"/>
+    <x v="19"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <x v="0"/>
+    <x v="20"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <x v="0"/>
+    <x v="21"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <x v="0"/>
+    <x v="22"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="23"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="24"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="25"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="26"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <x v="1"/>
+    <x v="27"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="28"/>
+    <n v="17"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="29"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="30"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="31"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <x v="2"/>
+    <x v="32"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <x v="2"/>
+    <x v="33"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <x v="2"/>
+    <x v="34"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <x v="2"/>
+    <x v="35"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <x v="2"/>
+    <x v="36"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <x v="2"/>
+    <x v="37"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <x v="3"/>
+    <x v="38"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <x v="3"/>
+    <x v="39"/>
+    <n v="33"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
     <n v="1.3"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="2"/>
     <x v="0"/>
     <n v="2.7"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="3"/>
     <x v="0"/>
     <n v="1.8"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="4"/>
     <x v="0"/>
     <n v="3.4"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="5"/>
     <x v="0"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="6"/>
     <x v="0"/>
     <n v="4.2"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="7"/>
     <x v="0"/>
     <n v="2.1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="8"/>
     <x v="0"/>
     <n v="5.8"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <n v="9"/>
     <x v="0"/>
     <n v="1.6"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="10"/>
     <x v="0"/>
     <n v="3.1"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="11"/>
     <x v="0"/>
     <n v="2.4"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="12"/>
     <x v="0"/>
     <n v="1.9"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="13"/>
     <x v="0"/>
     <n v="4.7"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="14"/>
     <x v="0"/>
     <n v="2.2999999999999998"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="15"/>
     <x v="0"/>
     <n v="1.4"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="16"/>
     <x v="0"/>
     <n v="3.8"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="17"/>
     <x v="0"/>
     <n v="5.2"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <n v="18"/>
     <x v="0"/>
     <n v="2.8"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="19"/>
     <x v="0"/>
     <n v="1.7"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="20"/>
     <x v="0"/>
     <n v="6.1"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <n v="21"/>
     <x v="0"/>
     <n v="2.2000000000000002"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="22"/>
     <x v="0"/>
     <n v="3.6"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="23"/>
     <x v="0"/>
     <n v="4.0999999999999996"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="24"/>
     <x v="1"/>
     <n v="7.3"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <n v="25"/>
     <x v="1"/>
     <n v="14.5"/>
-    <n v="12"/>
+    <x v="6"/>
   </r>
   <r>
     <n v="26"/>
     <x v="1"/>
     <n v="6.2"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <n v="27"/>
     <x v="1"/>
     <n v="22"/>
-    <n v="18"/>
+    <x v="7"/>
   </r>
   <r>
     <n v="28"/>
     <x v="1"/>
     <n v="9.8000000000000007"/>
-    <n v="8"/>
+    <x v="8"/>
   </r>
   <r>
     <n v="29"/>
     <x v="1"/>
     <n v="21.5"/>
-    <n v="17"/>
+    <x v="9"/>
   </r>
   <r>
     <n v="30"/>
     <x v="1"/>
     <n v="11.4"/>
-    <n v="10"/>
+    <x v="10"/>
   </r>
   <r>
     <n v="31"/>
     <x v="1"/>
     <n v="17.2"/>
-    <n v="14"/>
+    <x v="11"/>
   </r>
   <r>
     <n v="32"/>
     <x v="1"/>
     <n v="8.6"/>
-    <n v="7"/>
+    <x v="12"/>
   </r>
   <r>
     <n v="33"/>
     <x v="2"/>
     <n v="4.8"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="34"/>
     <x v="2"/>
     <n v="12.3"/>
-    <n v="10"/>
+    <x v="10"/>
   </r>
   <r>
     <n v="35"/>
     <x v="2"/>
     <n v="7.6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <n v="36"/>
     <x v="2"/>
     <n v="19.399999999999999"/>
-    <n v="15"/>
+    <x v="13"/>
   </r>
   <r>
     <n v="37"/>
     <x v="2"/>
     <n v="9.1"/>
-    <n v="8"/>
+    <x v="8"/>
   </r>
   <r>
     <n v="38"/>
     <x v="2"/>
     <n v="15.7"/>
-    <n v="13"/>
+    <x v="14"/>
   </r>
   <r>
     <n v="39"/>
     <x v="3"/>
     <n v="31.5"/>
-    <n v="28"/>
+    <x v="15"/>
   </r>
   <r>
     <n v="40"/>
     <x v="3"/>
     <n v="37.200000000000003"/>
+    <x v="16"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="24"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="25"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="26"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <x v="1"/>
+    <x v="27"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="28"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="29"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="30"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="31"/>
+    <x v="12"/>
+  </r>
+  <r>
     <n v="33"/>
+    <x v="2"/>
+    <x v="32"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <x v="2"/>
+    <x v="33"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <x v="2"/>
+    <x v="34"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <x v="2"/>
+    <x v="35"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <x v="2"/>
+    <x v="36"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <x v="2"/>
+    <x v="37"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <x v="3"/>
+    <x v="38"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <x v="3"/>
+    <x v="39"/>
+    <x v="16"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2B434DC-65F9-4D6F-8D32-3B6C6BD63910}" name="Tabela dinâmica6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A14:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Tempo de Resolução (h)" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE0BAC71-07C1-4C7C-9A63-C3C3FDB818E4}" name="Tabela dinâmica5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Tempo de Resolução (h)" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F481D76C-8C54-4CFA-9B94-B5F570B945BE}" name="Tabela dinâmica33" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sistemas Afetados">
-  <location ref="B18:E24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Frequência Simples" fld="2" subtotal="count" baseField="2" baseItem="0"/>
-    <dataField name="Frequência Percentual" fld="2" showDataAs="percentOfTotal" baseField="2" baseItem="0" numFmtId="10"/>
-    <dataField name="Frequência Acumulada" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F69093-ED37-46FC-B83E-B5405D647D84}" name="Tabela dinâmica32" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Resolução">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F69093-ED37-46FC-B83E-B5405D647D84}" name="Tabela dinâmica32" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Resolução">
   <location ref="B9:E16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0"/>
@@ -7152,8 +8504,84 @@
   <dataFields count="3">
     <dataField name="Frequência Simples" fld="1" subtotal="count" baseField="1" baseItem="0"/>
     <dataField name="Frequência Percentual" fld="1" subtotal="count" showDataAs="percentOfTotal" baseField="1" baseItem="0" numFmtId="10"/>
-    <dataField name="Frequência Acumulada" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Frequência Acumulada" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="1"/>
   </dataFields>
+  <formats count="12">
+    <format dxfId="65">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="64">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="6">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="59">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="6">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -7166,8 +8594,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10D43E93-EED9-4798-A5C4-2C2977AE21F0}" name="Tabela dinâmica21" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Tipo de Problema">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10D43E93-EED9-4798-A5C4-2C2977AE21F0}" name="Tabela dinâmica21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Tipo de Problema">
   <location ref="B2:E7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -7221,6 +8649,714 @@
     <dataField name="Frequência Percentual" fld="0" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
     <dataField name="Frequência Acumulada" fld="0" subtotal="count" showDataAs="runTotal" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="12">
+    <format dxfId="77">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="76">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="75">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="74">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="73">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="72">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="71">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="70">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="69">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F481D76C-8C54-4CFA-9B94-B5F570B945BE}" name="Tabela dinâmica33" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sistemas Afetados">
+  <location ref="B18:E24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Frequência Simples" fld="2" subtotal="count" baseField="2" baseItem="0"/>
+    <dataField name="Frequência Percentual" fld="2" showDataAs="percentOfTotal" baseField="2" baseItem="0" numFmtId="10"/>
+    <dataField name="Frequência Acumulada" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="1"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="89">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="88">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="87">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="86">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="5">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="85">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="84">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="83">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="82">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="81">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="5">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2A65A813-2297-469F-9756-C68FA2FAFD39}" name="Tabela dinâmica7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sistemas Afetados" colHeaderCaption="Tempo de Resolução">
+  <location ref="A18:E24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" numFmtId="164" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Sistemas Afetados" fld="3" subtotal="average" baseField="3" baseItem="0"/>
+  </dataFields>
+  <formats count="24">
+    <format dxfId="23">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E834750-A5B6-4ED5-BF40-6AB056730674}" name="Tabela dinâmica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sistemas Afetados">
+  <location ref="A10:E16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Sistemas Afetados" fld="3" subtotal="average" baseField="3" baseItem="0"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2B434DC-65F9-4D6F-8D32-3B6C6BD63910}" name="Tabela dinâmica6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Resolução">
+  <location ref="A2:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" numFmtId="164" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Tempo de Resolução (h)" fld="2" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <formats count="26">
+    <format dxfId="53">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="48">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -7517,130 +9653,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E57421-9380-4C29-84B3-4A21365C2F7E}">
-  <dimension ref="A3:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="44">
-        <v>68.900000000000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="44">
-        <v>118.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="44">
-        <v>69.199999999999989</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="44">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="44">
-        <v>325.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="44">
-        <v>68.900000000000006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="44">
-        <v>118.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="44">
-        <v>69.199999999999989</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="44">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="44">
-        <v>325.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="10" max="10" width="21.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7654,7 +9680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -7668,7 +9694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -7682,7 +9708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -7696,7 +9722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -7710,7 +9736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7724,7 +9750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -7738,7 +9764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7752,7 +9778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -7766,7 +9792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7780,7 +9806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -7794,7 +9820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7808,7 +9834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -7822,7 +9848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7836,7 +9862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -7850,7 +9876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -7864,7 +9890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -7878,7 +9904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7892,7 +9918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -7906,7 +9932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7920,7 +9946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -7934,7 +9960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7948,7 +9974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -7962,7 +9988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7976,7 +10002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -7990,7 +10016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>25</v>
       </c>
@@ -8004,7 +10030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -8018,7 +10044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>27</v>
       </c>
@@ -8032,7 +10058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -8046,7 +10072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>29</v>
       </c>
@@ -8059,22 +10085,8 @@
       <c r="D30" s="11">
         <v>17</v>
       </c>
-      <c r="F30" s="64"/>
-      <c r="G30" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K30" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="L30" s="63"/>
     </row>
-    <row r="31" spans="1:12" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -8087,639 +10099,667 @@
       <c r="D31" s="8">
         <v>10</v>
       </c>
-      <c r="F31" s="66" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>31</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="13">
+        <v>17.2</v>
+      </c>
+      <c r="D32" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="10">
+        <v>8.6</v>
+      </c>
+      <c r="D33" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="16">
+        <v>4.8</v>
+      </c>
+      <c r="D34" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
+        <v>34</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="19">
+        <v>12.3</v>
+      </c>
+      <c r="D35" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="16">
+        <v>7.6</v>
+      </c>
+      <c r="D36" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
+        <v>36</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="19">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D37" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="14">
+        <v>37</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="16">
+        <v>9.1</v>
+      </c>
+      <c r="D38" s="14">
         <v>8</v>
       </c>
-      <c r="G31" s="67">
+    </row>
+    <row r="39" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="17">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="19">
+        <v>15.7</v>
+      </c>
+      <c r="D39" s="17">
+        <v>13</v>
+      </c>
+      <c r="F39" s="46"/>
+      <c r="G39" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="L39" s="62"/>
+    </row>
+    <row r="40" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="20">
+        <v>39</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="22">
+        <v>31.5</v>
+      </c>
+      <c r="D40" s="20">
+        <v>28</v>
+      </c>
+      <c r="F40" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="49">
         <f>AVERAGE(C2:C41)</f>
         <v>8.1325000000000003</v>
       </c>
-      <c r="H31" s="67">
+      <c r="H40" s="49">
         <f>AVERAGE(D2:D41)</f>
         <v>6.875</v>
       </c>
-      <c r="J31" s="62" t="s">
+      <c r="J40" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="K31" s="63" t="s">
+      <c r="K40" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="L31" s="63"/>
+      <c r="L40" s="62"/>
     </row>
-    <row r="32" spans="1:12" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="11">
-        <v>31</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="13">
-        <v>17.2</v>
-      </c>
-      <c r="D32" s="11">
-        <v>14</v>
-      </c>
-      <c r="F32" s="66" t="s">
+    <row r="41" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="23">
+        <v>40</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="25">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D41" s="23">
+        <v>33</v>
+      </c>
+      <c r="F41" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="68">
+      <c r="G41" s="50">
         <f>MEDIAN(C2:C41)</f>
         <v>4.75</v>
       </c>
-      <c r="H32" s="69">
+      <c r="H41" s="51">
         <f>MEDIAN(D2:D41)</f>
         <v>4</v>
       </c>
-      <c r="J32" s="62" t="s">
+      <c r="J41" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="63" t="s">
+      <c r="K41" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="L32" s="63"/>
+      <c r="L41" s="62"/>
     </row>
-    <row r="33" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <v>32</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="10">
-        <v>8.6</v>
-      </c>
-      <c r="D33" s="8">
-        <v>7</v>
-      </c>
-      <c r="F33" s="66" t="s">
+    <row r="42" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="70" t="e" cm="1">
-        <f t="array" ref="G33">_xlfn.MODE.MULT(C2:C41)</f>
+      <c r="G42" s="52" t="e" cm="1">
+        <f t="array" ref="G42">_xlfn.MODE.MULT(C2:C41)</f>
         <v>#N/A</v>
       </c>
-      <c r="H33" s="70" cm="1">
-        <f t="array" ref="H33:H34">_xlfn.MODE.MULT(D2:D41)</f>
+      <c r="H42" s="52" cm="1">
+        <f t="array" ref="H42:H43">_xlfn.MODE.MULT(D2:D41)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="14">
-        <v>33</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="16">
-        <v>4.8</v>
-      </c>
-      <c r="D34" s="14">
-        <v>4</v>
-      </c>
-      <c r="F34" s="64"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="70">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F43" s="46"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="17">
-        <v>34</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="19">
-        <v>12.3</v>
-      </c>
-      <c r="D35" s="17">
-        <v>10</v>
-      </c>
-      <c r="F35" s="66" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F44" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="G35" s="72">
+      <c r="G44" s="54">
         <f>_xlfn.VAR.S(C2:C41)</f>
         <v>70.967891025641009</v>
       </c>
-      <c r="H35" s="73">
+      <c r="H44" s="55">
         <f>_xlfn.VAR.S(D2:D41)</f>
         <v>52.009615384615387</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="14">
-        <v>35</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="16">
-        <v>7.6</v>
-      </c>
-      <c r="D36" s="14">
-        <v>6</v>
-      </c>
-      <c r="F36" s="66" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F45" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="74">
+      <c r="G45" s="56">
         <f>_xlfn.STDEV.S(C2:C41)</f>
         <v>8.4242442406212916</v>
       </c>
-      <c r="H36" s="74">
+      <c r="H45" s="56">
         <f>_xlfn.STDEV.S(D2:D41)</f>
         <v>7.211769227077041</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="17">
-        <v>36</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="19">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="D37" s="17">
-        <v>15</v>
-      </c>
-      <c r="F37" s="66" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F46" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="72">
-        <f>(G36/G31)</f>
+      <c r="G46" s="54">
+        <f>(G45/G40)</f>
         <v>1.0358738691203555</v>
       </c>
-      <c r="H37" s="72">
-        <f>(H36/H31)</f>
+      <c r="H46" s="54">
+        <f>(H45/H40)</f>
         <v>1.0489846148475697</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="14">
-        <v>37</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="16">
-        <v>9.1</v>
-      </c>
-      <c r="D38" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="17">
-        <v>38</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="19">
-        <v>15.7</v>
-      </c>
-      <c r="D39" s="17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="20">
-        <v>39</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="22">
-        <v>31.5</v>
-      </c>
-      <c r="D40" s="20">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="23">
-        <v>40</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="25">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="D41" s="23">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB77F3E9-C1F7-4709-A984-D6A7D312BE49}">
   <dimension ref="B2:L24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="42" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="43" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="59">
         <v>6</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="61">
         <v>0.15</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="59">
         <v>6</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="43">
         <v>6</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="K3" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="44">
+      <c r="L3" s="43">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="43" t="s">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="59">
         <v>9</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="61">
         <v>0.22500000000000001</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="59">
         <v>15</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="43">
         <v>9</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="44">
+      <c r="L4" s="43">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="43" t="s">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="59">
         <v>23</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="61">
         <v>0.57499999999999996</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="59">
         <v>38</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="43">
         <v>23</v>
       </c>
-      <c r="K5" s="46" t="s">
+      <c r="K5" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="43" t="s">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="59">
         <v>2</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="61">
         <v>0.05</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="59">
         <v>40</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="43">
         <v>2</v>
       </c>
-      <c r="K6" s="46" t="s">
+      <c r="K6" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="43" t="s">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="59">
         <v>40</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="61">
         <v>1</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="K7" s="46" t="s">
+      <c r="E7" s="59"/>
+      <c r="K7" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="K8" s="46" t="s">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="K8" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="42" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="46" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="59">
         <v>25</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="61">
         <v>0.625</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="46" t="s">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="59">
         <v>7</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="61">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E11" s="44">
-        <v>7</v>
+      <c r="E11" s="59">
+        <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="46" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="59">
         <v>3</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="61">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="59">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="59">
         <v>3</v>
       </c>
+      <c r="D13" s="61">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E13" s="59">
+        <v>38</v>
+      </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="44">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="59">
+        <v>1</v>
+      </c>
+      <c r="D14" s="61">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E14" s="59">
+        <v>39</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="43">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="59">
+        <v>1</v>
+      </c>
+      <c r="D15" s="61">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E15" s="59">
+        <v>40</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="59">
+        <v>40</v>
+      </c>
+      <c r="D16" s="61">
+        <v>1</v>
+      </c>
+      <c r="E16" s="59"/>
+      <c r="G16" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="G17" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E13" s="44">
-        <v>3</v>
+      <c r="C18" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="43">
+        <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="44">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="59">
+        <v>27</v>
+      </c>
+      <c r="D19" s="61">
+        <v>0.29818181818181816</v>
+      </c>
+      <c r="E19" s="59">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="59">
+        <v>6</v>
+      </c>
+      <c r="D20" s="61">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="59">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="59">
+        <v>5</v>
+      </c>
+      <c r="D21" s="61">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E21" s="59">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="59">
         <v>1</v>
       </c>
-      <c r="D14" s="45">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E14" s="44">
+      <c r="D22" s="61">
+        <v>0.10181818181818182</v>
+      </c>
+      <c r="E22" s="59">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="59">
         <v>1</v>
       </c>
-      <c r="G14" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="44">
-        <v>27</v>
+      <c r="D23" s="61">
+        <v>0.12</v>
+      </c>
+      <c r="E23" s="59">
+        <v>40</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="44">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="59">
+        <v>40</v>
+      </c>
+      <c r="D24" s="61">
         <v>1</v>
       </c>
-      <c r="D15" s="45">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E15" s="44">
-        <v>1</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="44">
-        <v>40</v>
-      </c>
-      <c r="D16" s="45">
-        <v>1</v>
-      </c>
-      <c r="E16" s="44">
-        <v>40</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="G17" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="44">
-        <v>27</v>
-      </c>
-      <c r="D19" s="45">
-        <v>0.29818181818181816</v>
-      </c>
-      <c r="E19" s="44">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="44">
-        <v>6</v>
-      </c>
-      <c r="D20" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="E20" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="44">
-        <v>5</v>
-      </c>
-      <c r="D21" s="45">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E21" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="44">
-        <v>1</v>
-      </c>
-      <c r="D22" s="45">
-        <v>0.10181818181818182</v>
-      </c>
-      <c r="E22" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B23" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="44">
-        <v>1</v>
-      </c>
-      <c r="D23" s="45">
-        <v>0.12</v>
-      </c>
-      <c r="E23" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="44">
-        <v>40</v>
-      </c>
-      <c r="D24" s="45">
-        <v>1</v>
-      </c>
-      <c r="E24" s="44">
-        <v>40</v>
-      </c>
+      <c r="E24" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8727,12 +10767,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD1CBAC-448C-4DF3-9C62-3174844BB057}">
   <dimension ref="B18:L22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>16</v>
       </c>
@@ -8758,7 +10798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
         <v>17</v>
       </c>
@@ -8769,7 +10809,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="31">
-        <f>(F18-'Incidentes de Segurança'!G31)/'Incidentes de Segurança'!G36</f>
+        <f>(F18-'Incidentes de Segurança'!G40)/'Incidentes de Segurança'!G45</f>
         <v>2.7738393299808504</v>
       </c>
       <c r="H19" s="27" t="s">
@@ -8782,11 +10822,11 @@
         <v>23</v>
       </c>
       <c r="L19" s="31">
-        <f>(L18-'Incidentes de Segurança'!H31)/'Incidentes de Segurança'!H36</f>
+        <f>(L18-'Incidentes de Segurança'!H40)/'Incidentes de Segurança'!H45</f>
         <v>2.9292395991658826</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="33" t="s">
         <v>18</v>
       </c>
@@ -8800,7 +10840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
         <v>19</v>
       </c>
@@ -8826,7 +10866,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
         <v>20</v>
       </c>
@@ -8837,7 +10877,7 @@
         <v>23</v>
       </c>
       <c r="F22" s="31">
-        <f>(F21-'Incidentes de Segurança'!G31)/'Incidentes de Segurança'!G36</f>
+        <f>(F21-'Incidentes de Segurança'!G40)/'Incidentes de Segurança'!G45</f>
         <v>3.4504578891288489</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -8850,7 +10890,7 @@
         <v>23</v>
       </c>
       <c r="L22" s="31">
-        <f>(L21-'Incidentes de Segurança'!H31)/'Incidentes de Segurança'!H36</f>
+        <f>(L21-'Incidentes de Segurança'!H40)/'Incidentes de Segurança'!H45</f>
         <v>3.6225507468974527</v>
       </c>
     </row>
@@ -8860,23 +10900,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08055A8E-92DB-4F79-BD2D-B4F5B0ED551D}">
   <dimension ref="J2:N15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J2" s="26">
         <f>CORREL('Incidentes de Segurança'!C2:C41,'Incidentes de Segurança'!D2:D41)</f>
         <v>0.99698994421115827</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="49"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="65"/>
     </row>
-    <row r="4" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J4" s="39" t="s">
         <v>25</v>
       </c>
@@ -8886,7 +10926,7 @@
       </c>
       <c r="L4" s="36"/>
     </row>
-    <row r="5" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J5" s="40" t="s">
         <v>26</v>
       </c>
@@ -8896,7 +10936,7 @@
       </c>
       <c r="L5" s="29"/>
     </row>
-    <row r="6" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J6" s="41" t="s">
         <v>27</v>
       </c>
@@ -8908,44 +10948,44 @@
         <v>-6.6058765651601625E-2</v>
       </c>
     </row>
-    <row r="7" spans="10:14" x14ac:dyDescent="0.35">
-      <c r="J7" s="50" t="s">
+    <row r="7" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J7" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="51"/>
-      <c r="L7" s="52"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="68"/>
     </row>
-    <row r="9" spans="10:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J9" s="53" t="s">
+    <row r="9" spans="10:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="55"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="71"/>
     </row>
-    <row r="10" spans="10:14" x14ac:dyDescent="0.35">
-      <c r="J10" s="56"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="58"/>
+    <row r="10" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
     </row>
-    <row r="11" spans="10:14" x14ac:dyDescent="0.35">
-      <c r="J11" s="56"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="58"/>
+    <row r="11" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
     </row>
-    <row r="12" spans="10:14" x14ac:dyDescent="0.35">
-      <c r="J12" s="59"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="61"/>
+    <row r="12" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J12" s="75"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="76"/>
+      <c r="N12" s="77"/>
     </row>
-    <row r="15" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J15" s="37"/>
     </row>
   </sheetData>
@@ -8957,4 +10997,342 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E57421-9380-4C29-84B3-4A21365C2F7E}">
+  <dimension ref="A2:H28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="60">
+        <v>7.166666666666667</v>
+      </c>
+      <c r="C4" s="60">
+        <v>7.9749999999999996</v>
+      </c>
+      <c r="D4" s="60">
+        <v>3.0086956521739125</v>
+      </c>
+      <c r="E4" s="60"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="60">
+        <v>15.799999999999999</v>
+      </c>
+      <c r="C5" s="60">
+        <v>14.366666666666665</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59">
+        <v>21.75</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="60">
+        <v>11.483333333333333</v>
+      </c>
+      <c r="C8" s="60">
+        <v>13.166666666666666</v>
+      </c>
+      <c r="D8" s="60">
+        <v>3.0086956521739125</v>
+      </c>
+      <c r="E8" s="60">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="60">
+        <v>7</v>
+      </c>
+      <c r="C12" s="60">
+        <v>7.2</v>
+      </c>
+      <c r="D12" s="60">
+        <v>2.652173913043478</v>
+      </c>
+      <c r="E12" s="60"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="60">
+        <v>14</v>
+      </c>
+      <c r="C13" s="60">
+        <v>15.25</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="60">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="C16" s="60">
+        <v>10.777777777777779</v>
+      </c>
+      <c r="D16" s="60">
+        <v>2.652173913043478</v>
+      </c>
+      <c r="E16" s="60">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="60">
+        <v>3.5</v>
+      </c>
+      <c r="C20" s="60">
+        <v>10</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60">
+        <v>13.5</v>
+      </c>
+      <c r="D21" s="60">
+        <v>17.5</v>
+      </c>
+      <c r="E21" s="60"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59">
+        <v>28</v>
+      </c>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59">
+        <v>33</v>
+      </c>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="60">
+        <v>3.5</v>
+      </c>
+      <c r="C24" s="60">
+        <v>12.333333333333334</v>
+      </c>
+      <c r="D24" s="60">
+        <v>17.5</v>
+      </c>
+      <c r="E24" s="60">
+        <v>30.5</v>
+      </c>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>